--- a/files/Results_template.xlsx
+++ b/files/Results_template.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linus\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DD5D35-9724-4208-9E46-42138985E9F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAD767A-7F6C-477A-B6F6-54E8F14FBDF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{674B0EE0-15B2-4056-8471-DE221DF3E305}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{674B0EE0-15B2-4056-8471-DE221DF3E305}"/>
   </bookViews>
   <sheets>
-    <sheet name="Daten" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -440,18 +440,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFFB076-0CE9-4034-A160-3F3EBC4B9D19}">
   <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="1" customWidth="1"/>
-    <col min="4" max="9" width="15.77734375" style="1" customWidth="1"/>
-    <col min="10" max="11" width="11.5546875" style="1"/>
-    <col min="12" max="12" width="15.77734375" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="1" customWidth="1"/>
+    <col min="4" max="9" width="15.7109375" style="1" customWidth="1"/>
+    <col min="10" max="11" width="11.5703125" style="1"/>
+    <col min="12" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
